--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_179_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_179_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9326</v>
+        <v>1.2768</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0795</v>
+        <v>1.3901</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1469</v>
+        <v>-0.1133</v>
       </c>
       <c r="G2" t="n">
         <v>1.0675</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7585</v>
+        <v>-1.4143</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8962</v>
+        <v>-0.5856</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8623</v>
+        <v>-0.8287</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6112</v>
+        <v>1.033</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5121</v>
+        <v>4.1018</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9008</v>
+        <v>-3.0689</v>
       </c>
       <c r="G3" t="n">
         <v>1.9329</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8578</v>
+        <v>-1.4361</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8962</v>
+        <v>-0.3064</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9616</v>
+        <v>-1.1297</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.42</v>
+        <v>-1.393</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2502</v>
+        <v>-0.7947</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.8302</v>
+        <v>-0.5984</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2816</v>
+        <v>-0.2264</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5821</v>
+        <v>-0.7886</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6994</v>
+        <v>0.5621</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4516</v>
+        <v>0.9428</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6419</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8097</v>
+        <v>0.3546</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.17</v>
+        <v>-1.1692</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0597</v>
+        <v>-1.3767</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1103</v>
+        <v>0.2075</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6566</v>
+        <v>-0.4707</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9584</v>
+        <v>-0.5777</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3018</v>
+        <v>0.107</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6028</v>
+        <v>-1.4261</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1052</v>
+        <v>2.4377</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4975</v>
+        <v>-3.8638</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2264</v>
+        <v>1.2816</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7886</v>
+        <v>0.5821</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5621</v>
+        <v>0.6994</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9428</v>
+        <v>3.4516</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5881999999999999</v>
+        <v>2.6419</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3546</v>
+        <v>0.8097</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1692</v>
+        <v>-2.17</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3767</v>
+        <v>-2.0597</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2075</v>
+        <v>-0.1103</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6805</v>
+        <v>-0.1896</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8883</v>
+        <v>0.1458</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2078</v>
+        <v>-0.3354</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8774</v>
+        <v>-2.4906</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3408</v>
+        <v>1.4588</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.2182</v>
+        <v>-3.9494</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2089</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9004</v>
+        <v>-1.5136</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4832</v>
+        <v>-0.3653</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.4172</v>
+        <v>-1.1483</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4981</v>
+        <v>-2.7739</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3139</v>
+        <v>-0.7241</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1842</v>
+        <v>-2.0498</v>
       </c>
       <c r="G7" t="n">
         <v>-4.0417</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3689</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8883</v>
+        <v>-0.2985</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4806</v>
+        <v>-0.3462</v>
       </c>
       <c r="V7" t="n">
         <v>2.1444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5046</v>
+        <v>-3.4121</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2382</v>
+        <v>-0.8097</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2663</v>
+        <v>-2.6024</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7591</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6553</v>
+        <v>-1.5628</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2696</v>
+        <v>-0.841</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3857</v>
+        <v>-0.7218</v>
       </c>
       <c r="V8" t="n">
         <v>0.1418</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.971</v>
+        <v>-3.967</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8055</v>
+        <v>0.4936</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1656</v>
+        <v>-4.4606</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7529</v>
+        <v>-3.5322</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5485</v>
+        <v>-1.384</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2044</v>
+        <v>-2.1481</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5772</v>
+        <v>0.5312</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3564</v>
+        <v>-0.1646</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2208</v>
+        <v>0.6958</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3302</v>
+        <v>-4.0634</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9049</v>
+        <v>-1.2195</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4252</v>
+        <v>-2.8439</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.2473</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.639</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2095</v>
+        <v>-0.5946</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9006</v>
+        <v>-0.3418</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.2528</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8197</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3558</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4052</v>
+        <v>-4.8303</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0218</v>
+        <v>-2.6311</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.427</v>
+        <v>-2.1992</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5322</v>
+        <v>-1.7529</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.384</v>
+        <v>-0.5485</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1481</v>
+        <v>-1.2044</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5312</v>
+        <v>0.5772</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1646</v>
+        <v>0.3564</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6958</v>
+        <v>0.2208</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0634</v>
+        <v>-2.3302</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2195</v>
+        <v>-0.9049</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.8439</v>
+        <v>-1.4252</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-4.639</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0328</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8136</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2192</v>
+        <v>-0.7246</v>
       </c>
       <c r="V10" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.3558</v>
+      </c>
+      <c r="X10" t="n">
         <v>-0.5361</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.5361</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.6586</v>
+        <v>-9.197100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.116300000000001</v>
+        <v>-7.9237</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5423</v>
+        <v>-1.2734</v>
       </c>
       <c r="G11" t="n">
         <v>-5.4703</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6368</v>
+        <v>-1.1754</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2617</v>
+        <v>-1.069</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3752</v>
+        <v>-0.1063</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-27.5539</v>
+        <v>-27.1803</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.374700000000002</v>
+        <v>-3.001300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-24.179</v>
+        <v>-24.1792</v>
       </c>
       <c r="G12" t="n">
         <v>-13.7095</v>
@@ -1360,7 +1360,7 @@
         <v>-12.3881</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.321499999999999</v>
+        <v>-1.3215</v>
       </c>
       <c r="J12" t="n">
         <v>11.4718</v>
@@ -1369,7 +1369,7 @@
         <v>3.275500000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>8.196299999999999</v>
+        <v>8.196300000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-25.1813</v>
@@ -1378,7 +1378,7 @@
         <v>-15.6635</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.517700000000001</v>
+        <v>-9.5177</v>
       </c>
       <c r="P12" t="n">
         <v>-4.6391</v>
@@ -1390,16 +1390,16 @@
         <v>11.5977</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.0249</v>
+        <v>-9.651499999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.5381</v>
+        <v>-4.1646</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.486800000000001</v>
+        <v>-5.4868</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8197000000000001</v>
+        <v>0.8197000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>5.928200000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0042</v>
+        <v>5.7744</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7984</v>
+        <v>5.1789</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7942</v>
+        <v>0.5954</v>
       </c>
       <c r="G13" t="n">
-        <v>3.7436</v>
+        <v>4.0186</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5556</v>
+        <v>0.9807</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1879</v>
+        <v>3.0379</v>
       </c>
       <c r="J13" t="n">
-        <v>5.1911</v>
+        <v>5.7591</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3141</v>
+        <v>1.7176</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8771</v>
+        <v>4.0415</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4476</v>
+        <v>-1.7405</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7584</v>
+        <v>-0.7369</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6891</v>
+        <v>-1.0037</v>
       </c>
       <c r="P13" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0287</v>
+        <v>0.06</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6948</v>
+        <v>0.0435</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3339</v>
+        <v>0.0165</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3883</v>
+        <v>5.2178</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1656</v>
+        <v>5.8548</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2226</v>
+        <v>-0.6369</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9138</v>
+        <v>3.7436</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9504</v>
+        <v>2.5556</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0367</v>
+        <v>1.1879</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1103</v>
+        <v>5.1911</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0367</v>
+        <v>3.3141</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0736</v>
+        <v>1.8771</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1965</v>
+        <v>-1.4476</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0862</v>
+        <v>-0.7584</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1103</v>
+        <v>-0.6891</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>2.222</v>
+        <v>1.2423</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2151</v>
+        <v>0.7512</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0069</v>
+        <v>0.4911</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0331</v>
+        <v>4.7034</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4712</v>
+        <v>3.4579</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5618</v>
+        <v>1.2455</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0186</v>
+        <v>3.9138</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9807</v>
+        <v>3.9504</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0379</v>
+        <v>-0.0367</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7591</v>
+        <v>4.1103</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7176</v>
+        <v>4.0367</v>
       </c>
       <c r="L15" t="n">
-        <v>4.0415</v>
+        <v>0.0736</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7405</v>
+        <v>-0.1965</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7369</v>
+        <v>-0.0862</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0037</v>
+        <v>-0.1103</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6814</v>
+        <v>1.5371</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6642</v>
+        <v>0.5074</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0171</v>
+        <v>1.0297</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5361</v>
+        <v>-0.2836</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.515</v>
+        <v>3.1776</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6456</v>
+        <v>2.1738</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8694</v>
+        <v>1.0039</v>
       </c>
       <c r="G16" t="n">
         <v>1.8451</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5797</v>
+        <v>1.2423</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4312</v>
+        <v>0.9594</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1485</v>
+        <v>0.2829</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4028</v>
+        <v>2.9282</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5062</v>
+        <v>0.8178</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1033</v>
+        <v>2.1104</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3696</v>
+        <v>0.6431</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0155</v>
+        <v>2.1824</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3851</v>
+        <v>-1.5393</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9281</v>
+        <v>0.7036</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8571</v>
+        <v>1.7645</v>
       </c>
       <c r="L17" t="n">
-        <v>2.071</v>
+        <v>-1.0609</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5584</v>
+        <v>-0.0604</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8726</v>
+        <v>0.4179</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6859</v>
+        <v>-0.4783</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7859</v>
+        <v>1.3572</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.1142</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2078</v>
+        <v>1.243</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3999</v>
+        <v>2.5657</v>
       </c>
       <c r="E18" t="n">
-        <v>0.346</v>
+        <v>-0.5551</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0539</v>
+        <v>3.1208</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6431</v>
+        <v>-0.5895</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1824</v>
+        <v>-0.1814</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5393</v>
+        <v>-0.4081</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7036</v>
+        <v>-1.1689</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7645</v>
+        <v>-1.0819</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0609</v>
+        <v>-0.0871</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0604</v>
+        <v>0.5794</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4179</v>
+        <v>0.9005</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4783</v>
+        <v>-0.3211</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>0.829</v>
+        <v>1.3897</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3576</v>
+        <v>0.472</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1866</v>
+        <v>0.9177</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1653</v>
+        <v>2.4678</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4898</v>
+        <v>0.757</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3245</v>
+        <v>1.7108</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9467</v>
+        <v>1.2601</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9772</v>
+        <v>0.6243</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9239</v>
+        <v>0.6357</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6872</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7141</v>
+        <v>0.1849</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0269</v>
+        <v>0.746</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6339</v>
+        <v>0.3292</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7369</v>
+        <v>0.4395</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.897</v>
+        <v>-0.1103</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5759</v>
+        <v>0.8314</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3541</v>
+        <v>-0.0863</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2219</v>
+        <v>0.9177</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1583</v>
+        <v>2.302</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4031</v>
+        <v>3.5062</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7552</v>
+        <v>-1.2042</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2601</v>
+        <v>1.3696</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6243</v>
+        <v>-0.0155</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6357</v>
+        <v>1.3851</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9308999999999999</v>
+        <v>2.9281</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1849</v>
+        <v>0.8571</v>
       </c>
       <c r="L20" t="n">
-        <v>0.746</v>
+        <v>2.071</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3292</v>
+        <v>-1.5584</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4395</v>
+        <v>-0.8726</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1103</v>
+        <v>-0.6859</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5219</v>
+        <v>0.6851</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4402</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9621</v>
+        <v>0.107</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.82</v>
+        <v>2.1153</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6731</v>
+        <v>2.6078</v>
       </c>
       <c r="F21" t="n">
-        <v>2.493</v>
+        <v>-0.4925</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5895</v>
+        <v>-0.9467</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1814</v>
+        <v>0.9772</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4081</v>
+        <v>-1.9239</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1689</v>
+        <v>1.6872</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0819</v>
+        <v>1.7141</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0871</v>
+        <v>-0.0269</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5794</v>
+        <v>-2.6339</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9005</v>
+        <v>-0.7369</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3211</v>
+        <v>-1.897</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.644</v>
+        <v>0.5258</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3541</v>
+        <v>0.472</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2899</v>
+        <v>0.0538</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0325</v>
+        <v>0.2364</v>
       </c>
       <c r="E22" t="n">
         <v>-0.8231000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7906</v>
+        <v>1.0595</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6889</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8162</v>
+        <v>1.0851</v>
       </c>
       <c r="T22" t="n">
         <v>0.6607</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1555</v>
+        <v>0.4244</v>
       </c>
       <c r="V22" t="n">
         <v>0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7611</v>
+        <v>-0.5924</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5026</v>
+        <v>-0.2667</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2585</v>
+        <v>-0.3257</v>
       </c>
       <c r="G23" t="n">
         <v>0.2169</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2539</v>
+        <v>0.4226</v>
       </c>
       <c r="T23" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.3185</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5395</v>
+        <v>-2.556</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3518</v>
+        <v>1.4697</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8913</v>
+        <v>-4.0257</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0761</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>0.449</v>
+        <v>0.4325</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1291</v>
+        <v>-0.2636</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1444</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>27.5538</v>
+        <v>28.3402</v>
       </c>
       <c r="E25" t="n">
-        <v>24.1789</v>
+        <v>24.179</v>
       </c>
       <c r="F25" t="n">
-        <v>3.3747</v>
+        <v>4.161300000000002</v>
       </c>
       <c r="G25" t="n">
         <v>13.7096</v>
@@ -2374,7 +2374,7 @@
         <v>12.3879</v>
       </c>
       <c r="I25" t="n">
-        <v>1.321400000000001</v>
+        <v>1.321399999999999</v>
       </c>
       <c r="J25" t="n">
         <v>25.1814</v>
@@ -2404,16 +2404,16 @@
         <v>16.2367</v>
       </c>
       <c r="S25" t="n">
-        <v>10.0248</v>
+        <v>10.8111</v>
       </c>
       <c r="T25" t="n">
         <v>5.486800000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>4.538200000000001</v>
+        <v>5.3243</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.8196999999999999</v>
+        <v>-0.8197000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>5.1085</v>
